--- a/data/美股體檢總表.xlsx
+++ b/data/美股體檢總表.xlsx
@@ -555,11 +555,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
         <v>17.7</v>
@@ -567,8 +567,12 @@
       <c r="G2" t="n">
         <v>33.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19.2</v>
+      </c>
       <c r="J2" t="n">
         <v>1.25</v>
       </c>
@@ -616,11 +620,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
         <v>17.7</v>
@@ -628,8 +632,12 @@
       <c r="G3" t="n">
         <v>33.5</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>39</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="J3" t="n">
         <v>1.25</v>
       </c>
@@ -677,11 +685,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
@@ -689,8 +697,12 @@
       <c r="G4" t="n">
         <v>12.2</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21.3</v>
+      </c>
       <c r="J4" t="n">
         <v>1.34</v>
       </c>
@@ -738,11 +750,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
         <v>14.4</v>
@@ -750,8 +762,12 @@
       <c r="G5" t="n">
         <v>40.6</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
       <c r="J5" t="n">
         <v>1.92</v>
       </c>
@@ -803,11 +819,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
         <v>30.8</v>
@@ -815,8 +831,12 @@
       <c r="G6" t="n">
         <v>18.8</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.8</v>
+      </c>
       <c r="J6" t="n">
         <v>1.37</v>
       </c>
@@ -864,11 +884,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
         <v>23.6</v>
@@ -876,8 +896,12 @@
       <c r="G7" t="n">
         <v>11.5</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
       <c r="J7" t="n">
         <v>2.18</v>
       </c>
@@ -929,11 +953,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>13.4</v>
@@ -941,8 +965,12 @@
       <c r="G8" t="n">
         <v>18.2</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.4</v>
+      </c>
       <c r="J8" t="n">
         <v>1.41</v>
       </c>
@@ -990,11 +1018,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
         <v>39.8</v>
@@ -1002,8 +1030,12 @@
       <c r="G9" t="n">
         <v>34.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
       <c r="J9" t="n">
         <v>1.72</v>
       </c>
@@ -1055,11 +1087,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
         <v>30.7</v>
@@ -1067,8 +1099,12 @@
       <c r="G10" t="n">
         <v>21.4</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.6</v>
+      </c>
       <c r="J10" t="n">
         <v>1.25</v>
       </c>
@@ -1105,46 +1141,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>PayPal Holdings, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>55.6</v>
+        <v>11.4</v>
       </c>
       <c r="G11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+        <v>37.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15.2</v>
+      </c>
       <c r="J11" t="n">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>46.6</v>
       </c>
       <c r="L11" t="n">
-        <v>20.1</v>
+        <v>15.8</v>
       </c>
       <c r="M11" t="n">
-        <v>25.2</v>
+        <v>6.9</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1160,52 +1200,60 @@
         <v>0</v>
       </c>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PayPal Holdings, Inc.</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+        <v>23.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>16.2</v>
+      </c>
       <c r="J12" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="K12" t="n">
-        <v>46.6</v>
+        <v>80.8</v>
       </c>
       <c r="L12" t="n">
-        <v>15.8</v>
+        <v>20.5</v>
       </c>
       <c r="M12" t="n">
-        <v>6.9</v>
+        <v>18.2</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1221,11 +1269,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1246,11 +1290,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
         <v>18.7</v>
@@ -1258,8 +1302,12 @@
       <c r="G13" t="n">
         <v>20.9</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.1</v>
+      </c>
       <c r="J13" t="n">
         <v>1.5</v>
       </c>
@@ -1292,46 +1340,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fair Isaac Corporation</t>
+          <t>The Hartford Insurance Group, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="G14" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+        <v>34.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>29.2</v>
+      </c>
       <c r="J14" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="K14" t="n">
-        <v>82.2</v>
+        <v>46.1</v>
       </c>
       <c r="L14" t="n">
-        <v>32.7</v>
+        <v>13.6</v>
       </c>
       <c r="M14" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1353,46 +1405,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>The Travelers Companies, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="G15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+        <v>32.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15.7</v>
+      </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="K15" t="n">
-        <v>80.8</v>
+        <v>44.3</v>
       </c>
       <c r="L15" t="n">
-        <v>20.5</v>
+        <v>12.9</v>
       </c>
       <c r="M15" t="n">
-        <v>18.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1414,46 +1470,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Travelers Companies, Inc.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>17.5</v>
+        <v>11.3</v>
       </c>
       <c r="G16" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+        <v>62.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20.1</v>
+      </c>
       <c r="J16" t="n">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>44.3</v>
+        <v>92.8</v>
       </c>
       <c r="L16" t="n">
-        <v>12.9</v>
+        <v>25</v>
       </c>
       <c r="M16" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1469,18 +1529,22 @@
         <v>0</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford Insurance Group, Inc.</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1490,31 +1554,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>19.1</v>
+        <v>35.7</v>
       </c>
       <c r="G17" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+        <v>153.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="K17" t="n">
-        <v>46.1</v>
+        <v>29.5</v>
       </c>
       <c r="L17" t="n">
-        <v>13.6</v>
+        <v>12.9</v>
       </c>
       <c r="M17" t="n">
-        <v>6.9</v>
+        <v>16.4</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1530,52 +1598,60 @@
         <v>0</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>35.7</v>
+        <v>40.8</v>
       </c>
       <c r="G18" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+        <v>51.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>32.1</v>
+      </c>
       <c r="J18" t="n">
-        <v>1.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>29.5</v>
+        <v>83.8</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9</v>
+        <v>31.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.4</v>
+        <v>23.2</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1591,56 +1667,56 @@
         <v>0</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>11.3</v>
+        <v>22.1</v>
       </c>
       <c r="G19" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+        <v>36.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23.1</v>
+      </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="K19" t="n">
-        <v>92.8</v>
+        <v>48.5</v>
       </c>
       <c r="L19" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="M19" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1656,56 +1732,56 @@
         <v>0</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>22.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+        <v>201.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>63</v>
+      </c>
       <c r="J20" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="K20" t="n">
-        <v>48.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>24.3</v>
+        <v>55.6</v>
       </c>
       <c r="M20" t="n">
-        <v>11.1</v>
+        <v>68.3</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1721,23 +1797,27 @@
         <v>0</v>
       </c>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1746,27 +1826,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>88.59999999999999</v>
+        <v>32.3</v>
       </c>
       <c r="G21" t="n">
-        <v>201.4</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13.5</v>
+      </c>
       <c r="J21" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>71.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="L21" t="n">
-        <v>55.6</v>
+        <v>21.5</v>
       </c>
       <c r="M21" t="n">
-        <v>68.3</v>
+        <v>9</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1792,17 +1876,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1811,27 +1895,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>40.8</v>
+        <v>55.6</v>
       </c>
       <c r="G22" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+        <v>29.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-95.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>68.2</v>
+      </c>
       <c r="J22" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="K22" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>31.7</v>
+        <v>20.1</v>
       </c>
       <c r="M22" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1848,22 +1936,26 @@
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ROE-95.8低</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1872,27 +1964,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+        <v>5.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>39</v>
+      </c>
+      <c r="I23" t="n">
+        <v>13.5</v>
+      </c>
       <c r="J23" t="n">
-        <v>1.23</v>
+        <v>2.01</v>
       </c>
       <c r="K23" t="n">
-        <v>57.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>31.9</v>
+        <v>14.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1908,52 +2004,60 @@
         <v>0</v>
       </c>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
-        <v>32.3</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15.5</v>
+      </c>
       <c r="J24" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="K24" t="n">
-        <v>47.7</v>
+        <v>51.2</v>
       </c>
       <c r="L24" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1969,22 +2073,18 @@
         <v>0</v>
       </c>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1994,31 +2094,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="G25" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>21.8</v>
+      </c>
       <c r="J25" t="n">
-        <v>1.86</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
-        <v>41.5</v>
+        <v>70.5</v>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>28.2</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2040,12 +2144,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2055,31 +2159,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F26" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="G26" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+        <v>23.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>20.3</v>
+      </c>
       <c r="J26" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="K26" t="n">
-        <v>70.5</v>
+        <v>78.8</v>
       </c>
       <c r="L26" t="n">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2095,52 +2203,60 @@
         <v>0</v>
       </c>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Fair Isaac Corporation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>18.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+        <v>23.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>53.2</v>
+      </c>
       <c r="J27" t="n">
-        <v>2.01</v>
+        <v>1.19</v>
       </c>
       <c r="K27" t="n">
-        <v>67.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L27" t="n">
-        <v>14.6</v>
+        <v>32.7</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2156,56 +2272,60 @@
         <v>0</v>
       </c>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>ROE-43.1低</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F28" t="n">
-        <v>8.4</v>
+        <v>12.7</v>
       </c>
       <c r="G28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>19</v>
+      </c>
       <c r="J28" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="K28" t="n">
-        <v>78.8</v>
+        <v>12.8</v>
       </c>
       <c r="L28" t="n">
-        <v>28.9</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2221,22 +2341,18 @@
         <v>0</v>
       </c>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2246,31 +2362,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F29" t="n">
-        <v>4.1</v>
+        <v>13.9</v>
       </c>
       <c r="G29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+        <v>24.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J29" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="K29" t="n">
-        <v>51.2</v>
+        <v>24.9</v>
       </c>
       <c r="L29" t="n">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2292,12 +2412,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2307,31 +2427,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F30" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="G30" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+        <v>18.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
       <c r="J30" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="K30" t="n">
-        <v>29.4</v>
+        <v>59.9</v>
       </c>
       <c r="L30" t="n">
-        <v>17.2</v>
+        <v>20.4</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2352,51 +2476,59 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EPS落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>EMCOR Group, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F31" t="n">
-        <v>6.9</v>
+        <v>41.2</v>
       </c>
       <c r="G31" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+        <v>51.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.7</v>
+      </c>
       <c r="J31" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>59.9</v>
+        <v>19.6</v>
       </c>
       <c r="L31" t="n">
-        <v>20.4</v>
+        <v>7.5</v>
       </c>
       <c r="M31" t="n">
-        <v>21.8</v>
+        <v>14.4</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2412,60 +2544,56 @@
         <v>0</v>
       </c>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>EPS落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>51.5</v>
+        <v>7.5</v>
       </c>
       <c r="G32" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+        <v>27.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J32" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="K32" t="n">
-        <v>3.6</v>
+        <v>29.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>17.2</v>
       </c>
       <c r="M32" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2491,12 +2619,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2506,31 +2634,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F33" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="G33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-433.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>17.4</v>
+      </c>
       <c r="J33" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="K33" t="n">
-        <v>51.6</v>
+        <v>57.4</v>
       </c>
       <c r="L33" t="n">
-        <v>14.3</v>
+        <v>31.9</v>
       </c>
       <c r="M33" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2547,51 +2679,59 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>ROE-433.9低</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Ameriprise Financial, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F34" t="n">
-        <v>12.7</v>
+        <v>6.1</v>
       </c>
       <c r="G34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.7</v>
+      </c>
       <c r="J34" t="n">
-        <v>1.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>12.8</v>
+        <v>50.4</v>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>18.8</v>
       </c>
       <c r="M34" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2613,12 +2753,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2632,27 +2772,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I35" t="n">
         <v>13.9</v>
       </c>
-      <c r="G35" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1.9</v>
+        <v>0.57</v>
       </c>
       <c r="K35" t="n">
-        <v>24.9</v>
+        <v>61.6</v>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>27.3</v>
       </c>
       <c r="M35" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2669,22 +2813,26 @@
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>含金量0.57弱</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2693,27 +2841,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F36" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="G36" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+        <v>13.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-123.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18.8</v>
+      </c>
       <c r="J36" t="n">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="K36" t="n">
-        <v>67.09999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="L36" t="n">
-        <v>27.9</v>
+        <v>9</v>
       </c>
       <c r="M36" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2730,22 +2882,26 @@
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>ROE-123.2低</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMCOR Group, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2754,27 +2910,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
-        <v>41.2</v>
+        <v>51.5</v>
       </c>
       <c r="G37" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>15.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-265.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.1</v>
+      </c>
       <c r="J37" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="K37" t="n">
-        <v>19.6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>14.4</v>
+        <v>11.2</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2790,23 +2950,31 @@
         <v>0</v>
       </c>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>ROE-265.4低</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ameriprise Financial, Inc.</t>
+          <t>General Dynamics Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2815,27 +2983,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="G38" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10.8</v>
+      </c>
       <c r="J38" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="K38" t="n">
-        <v>50.4</v>
+        <v>15.1</v>
       </c>
       <c r="L38" t="n">
-        <v>18.8</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2857,46 +3029,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Cigna Corporation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>7.6</v>
+      </c>
       <c r="J39" t="n">
-        <v>0.57</v>
+        <v>1.61</v>
       </c>
       <c r="K39" t="n">
-        <v>61.6</v>
+        <v>9.5</v>
       </c>
       <c r="L39" t="n">
-        <v>27.3</v>
+        <v>2.2</v>
       </c>
       <c r="M39" t="n">
-        <v>5.5</v>
+        <v>12.1</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2912,56 +3088,60 @@
         <v>0</v>
       </c>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>含金量0.57弱</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Dynamics Corporation</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F40" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-263.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>34.1</v>
+      </c>
       <c r="J40" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="K40" t="n">
-        <v>15.1</v>
+        <v>51.6</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>14.3</v>
       </c>
       <c r="M40" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -2978,51 +3158,59 @@
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>ROE-263.2低</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The PNC Financial Services Group, Inc.</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F41" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="G41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+        <v>7.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-105.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>24.3</v>
+      </c>
       <c r="J41" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="K41" t="n">
-        <v>71.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>22.1</v>
+        <v>27.9</v>
       </c>
       <c r="M41" t="n">
-        <v>12.3</v>
+        <v>6.7</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3041,19 +3229,19 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>含金量0.63弱</t>
+          <t>ROE-105.3低</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Cincinnati Financial Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3063,31 +3251,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+        <v>-4.6</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>18</v>
+      </c>
+      <c r="I42" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J42" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="K42" t="n">
-        <v>62.8</v>
+        <v>50.1</v>
       </c>
       <c r="L42" t="n">
-        <v>17.7</v>
+        <v>18.9</v>
       </c>
       <c r="M42" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3110,53 +3300,57 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cigna Corporation</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F43" t="n">
-        <v>8.800000000000001</v>
+        <v>-2.5</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.7</v>
+      </c>
       <c r="J43" t="n">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="K43" t="n">
-        <v>9.5</v>
+        <v>62.8</v>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>17.7</v>
       </c>
       <c r="M43" t="n">
-        <v>12.1</v>
+        <v>15.9</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3177,17 +3371,21 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation</t>
+          <t>The PNC Financial Services Group, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3197,29 +3395,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
       <c r="J44" t="n">
-        <v>1.3</v>
+        <v>0.63</v>
       </c>
       <c r="K44" t="n">
-        <v>50.1</v>
+        <v>71.7</v>
       </c>
       <c r="L44" t="n">
-        <v>18.9</v>
+        <v>22.1</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3235,26 +3439,22 @@
         <v>0</v>
       </c>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>EPS資料不足、EPS落後營收(稀釋/毛利漏)</t>
+          <t>含金量0.63弱</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>The Allstate Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3264,31 +3464,33 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G45" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+        <v>21.9</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.2</v>
+      </c>
       <c r="J45" t="n">
-        <v>-0.89</v>
+        <v>0.98</v>
       </c>
       <c r="K45" t="n">
-        <v>64.8</v>
+        <v>33.2</v>
       </c>
       <c r="L45" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="M45" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -3311,51 +3513,57 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>含金量-0.89差</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Allstate Corporation</t>
+          <t>Cencora, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J46" t="n">
-        <v>0.98</v>
+        <v>2.49</v>
       </c>
       <c r="K46" t="n">
-        <v>33.2</v>
+        <v>3.2</v>
       </c>
       <c r="L46" t="n">
-        <v>15.5</v>
+        <v>0.5</v>
       </c>
       <c r="M46" t="n">
-        <v>8.1</v>
+        <v>10.7</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3378,51 +3586,57 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cardinal Health, Inc.</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.1</v>
+      </c>
       <c r="J47" t="n">
-        <v>1.54</v>
+        <v>-0.89</v>
       </c>
       <c r="K47" t="n">
-        <v>3.7</v>
+        <v>64.8</v>
       </c>
       <c r="L47" t="n">
-        <v>0.7</v>
+        <v>17.3</v>
       </c>
       <c r="M47" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3445,24 +3659,24 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>含金量-0.89差</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cencora, Inc.</t>
+          <t>Aflac Incorporated</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3471,27 +3685,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G48" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J48" t="n">
-        <v>2.49</v>
+        <v>0.7</v>
       </c>
       <c r="K48" t="n">
-        <v>3.2</v>
+        <v>38.9</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5</v>
+        <v>20.9</v>
       </c>
       <c r="M48" t="n">
-        <v>10.7</v>
+        <v>-5.2</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -3514,19 +3732,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收萎縮-5.2%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aflac Incorporated</t>
+          <t>T. Rowe Price Group, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3540,27 +3758,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>1.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>12.4</v>
+      </c>
       <c r="J49" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="K49" t="n">
-        <v>38.9</v>
+        <v>62.7</v>
       </c>
       <c r="L49" t="n">
-        <v>20.9</v>
+        <v>28.5</v>
       </c>
       <c r="M49" t="n">
-        <v>-5.2</v>
+        <v>-1.2</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3583,24 +3805,24 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收萎縮-5.2%</t>
+          <t>EPS單期衰退、營收萎縮-1.2%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T. Rowe Price Group, Inc.</t>
+          <t>Northrop Grumman Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3609,27 +3831,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F50" t="n">
-        <v>-8.6</v>
+        <v>-9.6</v>
       </c>
       <c r="G50" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+        <v>-2.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J50" t="n">
-        <v>0.84</v>
+        <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>62.7</v>
+        <v>19.8</v>
       </c>
       <c r="L50" t="n">
-        <v>28.5</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -3652,24 +3878,24 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收萎縮-1.2%</t>
+          <t>EPS連年衰退、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Prudential Financial, Inc.</t>
+          <t>Cardinal Health, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3678,25 +3904,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F51" t="n">
-        <v>-18.1</v>
+        <v>32.7</v>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>-55.7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11.6</v>
+      </c>
       <c r="J51" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="K51" t="n">
-        <v>42</v>
+        <v>3.7</v>
       </c>
       <c r="L51" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="M51" t="n">
-        <v>-3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3719,24 +3949,24 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收萎縮-3.9%</t>
+          <t>EPS資料不足、ROE-55.7低</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corporation</t>
+          <t>Prudential Financial, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3745,27 +3975,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+        <v>-18.1</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J52" t="n">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="K52" t="n">
-        <v>19.8</v>
+        <v>42</v>
       </c>
       <c r="L52" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="M52" t="n">
-        <v>4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -3788,7 +4020,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收萎縮-3.9%</t>
         </is>
       </c>
     </row>
@@ -3803,7 +4035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3922,6 +4154,1273 @@
           <t>主要漏洞</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>39</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Autodesk, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K7" t="n">
+        <v>91</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adobe Inc.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DXCM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DexCom, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RMD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ResMed Inc.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PayPal Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Intuit Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>86</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Linde plc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>83</v>
+      </c>
+      <c r="F13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Hartford Insurance Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K14" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Travelers Companies, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>83</v>
+      </c>
+      <c r="F15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K15" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INCY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Incyte Corporation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PGR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Progressive Corporation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>82</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K19" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>63</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4203,11 +5702,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
         <v>14.4</v>
@@ -4215,8 +5714,12 @@
       <c r="G2" t="n">
         <v>40.6</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
       <c r="J2" t="n">
         <v>1.92</v>
       </c>
@@ -4268,11 +5771,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
         <v>23.6</v>
@@ -4280,8 +5783,12 @@
       <c r="G3" t="n">
         <v>11.5</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
       <c r="J3" t="n">
         <v>2.18</v>
       </c>
@@ -4333,11 +5840,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>39.8</v>
@@ -4345,8 +5852,12 @@
       <c r="G4" t="n">
         <v>34.5</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18</v>
+      </c>
       <c r="J4" t="n">
         <v>1.72</v>
       </c>
@@ -4398,11 +5909,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
         <v>30.7</v>
@@ -4410,8 +5921,12 @@
       <c r="G5" t="n">
         <v>21.4</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19.6</v>
+      </c>
       <c r="J5" t="n">
         <v>1.25</v>
       </c>
@@ -4463,11 +5978,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
         <v>11.4</v>
@@ -4475,8 +5990,12 @@
       <c r="G6" t="n">
         <v>37.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.2</v>
+      </c>
       <c r="J6" t="n">
         <v>1.23</v>
       </c>
@@ -4513,46 +6032,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
-        <v>35.7</v>
+        <v>11.3</v>
       </c>
       <c r="G7" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>62.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.1</v>
+      </c>
       <c r="J7" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>29.5</v>
+        <v>92.8</v>
       </c>
       <c r="L7" t="n">
-        <v>12.9</v>
+        <v>25</v>
       </c>
       <c r="M7" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -4578,46 +6101,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3</v>
+        <v>35.7</v>
       </c>
       <c r="G8" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>153.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="K8" t="n">
-        <v>92.8</v>
+        <v>29.5</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="M8" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -4658,11 +6185,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
         <v>88.59999999999999</v>
@@ -4670,8 +6197,12 @@
       <c r="G9" t="n">
         <v>201.4</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>63</v>
+      </c>
       <c r="J9" t="n">
         <v>0.86</v>
       </c>
@@ -4723,11 +6254,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
         <v>32.3</v>
@@ -4735,8 +6266,12 @@
       <c r="G10" t="n">
         <v>11.9</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13.5</v>
+      </c>
       <c r="J10" t="n">
         <v>0.9399999999999999</v>
       </c>
@@ -4788,11 +6323,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
         <v>2.4</v>
@@ -4800,8 +6335,12 @@
       <c r="G11" t="n">
         <v>5.2</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13.5</v>
+      </c>
       <c r="J11" t="n">
         <v>2.01</v>
       </c>
@@ -4853,11 +6392,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
         <v>8.4</v>
@@ -4865,8 +6404,12 @@
       <c r="G12" t="n">
         <v>23.2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20.3</v>
+      </c>
       <c r="J12" t="n">
         <v>1.18</v>
       </c>
@@ -4903,12 +6446,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4918,31 +6461,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="G13" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+        <v>18.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
       <c r="J13" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="K13" t="n">
-        <v>29.4</v>
+        <v>59.9</v>
       </c>
       <c r="L13" t="n">
-        <v>17.2</v>
+        <v>20.4</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -4963,17 +6510,21 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>EPS落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4983,31 +6534,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="G14" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+        <v>27.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J14" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="K14" t="n">
-        <v>59.9</v>
+        <v>29.4</v>
       </c>
       <c r="L14" t="n">
-        <v>20.4</v>
+        <v>17.2</v>
       </c>
       <c r="M14" t="n">
-        <v>21.8</v>
+        <v>10</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -5028,11 +6583,7 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>EPS落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5064,8 +6615,12 @@
       <c r="G15" t="n">
         <v>15.2</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>-265.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>31.1</v>
+      </c>
       <c r="J15" t="n">
         <v>1.29</v>
       </c>
@@ -5097,51 +6652,59 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ROE-265.4低</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Cigna Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7.6</v>
+      </c>
       <c r="J16" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="K16" t="n">
-        <v>62.8</v>
+        <v>9.5</v>
       </c>
       <c r="L16" t="n">
-        <v>17.7</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.9</v>
+        <v>12.1</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -5162,55 +6725,53 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cigna Corporation</t>
+          <t>Cincinnati Financial Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+        <v>-4.6</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J17" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>9.5</v>
+        <v>50.1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>18.9</v>
       </c>
       <c r="M17" t="n">
-        <v>12.1</v>
+        <v>7</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -5231,17 +6792,21 @@
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>EPS資料不足、EPS落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5251,29 +6816,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.7</v>
+      </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="K18" t="n">
-        <v>50.1</v>
+        <v>62.8</v>
       </c>
       <c r="L18" t="n">
-        <v>18.9</v>
+        <v>17.7</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>15.9</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -5296,19 +6867,19 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>EPS資料不足、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>The Allstate Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5318,31 +6889,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+        <v>21.9</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.2</v>
+      </c>
       <c r="J19" t="n">
-        <v>-0.89</v>
+        <v>0.98</v>
       </c>
       <c r="K19" t="n">
-        <v>64.8</v>
+        <v>33.2</v>
       </c>
       <c r="L19" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="M19" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -5365,51 +6938,57 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>含金量-0.89差</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Allstate Corporation</t>
+          <t>Cencora, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J20" t="n">
-        <v>0.98</v>
+        <v>2.49</v>
       </c>
       <c r="K20" t="n">
-        <v>33.2</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>15.5</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>8.1</v>
+        <v>10.7</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -5432,51 +7011,57 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cardinal Health, Inc.</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
       <c r="J21" t="n">
-        <v>1.54</v>
+        <v>-0.89</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>64.8</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>17.3</v>
       </c>
       <c r="M21" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -5499,24 +7084,24 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>含金量-0.89差</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cencora, Inc.</t>
+          <t>Aflac Incorporated</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5525,27 +7110,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J22" t="n">
-        <v>2.49</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>38.9</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>20.9</v>
       </c>
       <c r="M22" t="n">
-        <v>10.7</v>
+        <v>-5.2</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -5568,19 +7157,19 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收萎縮-5.2%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aflac Incorporated</t>
+          <t>T. Rowe Price Group, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5594,27 +7183,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12.4</v>
+      </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="K23" t="n">
-        <v>38.9</v>
+        <v>62.7</v>
       </c>
       <c r="L23" t="n">
-        <v>20.9</v>
+        <v>28.5</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.2</v>
+        <v>-1.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -5637,24 +7230,24 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收萎縮-5.2%</t>
+          <t>EPS單期衰退、營收萎縮-1.2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T. Rowe Price Group, Inc.</t>
+          <t>Northrop Grumman Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5663,27 +7256,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.6</v>
+        <v>-9.6</v>
       </c>
       <c r="G24" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+        <v>-2.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.3</v>
+      </c>
       <c r="J24" t="n">
-        <v>0.84</v>
+        <v>1.14</v>
       </c>
       <c r="K24" t="n">
-        <v>62.7</v>
+        <v>19.8</v>
       </c>
       <c r="L24" t="n">
-        <v>28.5</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -5706,24 +7303,24 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收萎縮-1.2%</t>
+          <t>EPS連年衰退、EPS落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prudential Financial, Inc.</t>
+          <t>Cardinal Health, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5732,25 +7329,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.1</v>
+        <v>32.7</v>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>-55.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.6</v>
+      </c>
       <c r="J25" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="K25" t="n">
-        <v>42</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -5773,24 +7374,24 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收萎縮-3.9%</t>
+          <t>EPS資料不足、ROE-55.7低</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corporation</t>
+          <t>Prudential Financial, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5799,27 +7400,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+        <v>-18.1</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J26" t="n">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="K26" t="n">
-        <v>19.8</v>
+        <v>42</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -5842,7 +7445,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收萎縮-3.9%</t>
         </is>
       </c>
     </row>

--- a/data/美股體檢總表.xlsx
+++ b/data/美股體檢總表.xlsx
@@ -585,7 +585,9 @@
       <c r="M2" t="n">
         <v>11.8</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>31.8</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -596,7 +598,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -650,7 +652,9 @@
       <c r="M3" t="n">
         <v>11.8</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -661,7 +665,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -715,7 +719,9 @@
       <c r="M4" t="n">
         <v>13.8</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>27.3</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -726,7 +732,7 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -780,7 +786,9 @@
       <c r="M5" t="n">
         <v>14.3</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>23.5</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -791,7 +799,7 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -849,7 +857,9 @@
       <c r="M6" t="n">
         <v>24.8</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -860,7 +870,7 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -914,7 +924,9 @@
       <c r="M7" t="n">
         <v>13.2</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>35.7</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -983,7 +995,9 @@
       <c r="M8" t="n">
         <v>10.8</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1048,7 +1062,9 @@
       <c r="M9" t="n">
         <v>17.5</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>32.2</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1117,7 +1133,9 @@
       <c r="M10" t="n">
         <v>12.6</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1128,7 +1146,7 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
@@ -1186,7 +1204,9 @@
       <c r="M11" t="n">
         <v>6.9</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>7.7</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1197,7 +1217,7 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -1255,7 +1275,9 @@
       <c r="M12" t="n">
         <v>18.2</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>18.7</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1266,7 +1288,7 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1320,7 +1342,9 @@
       <c r="M13" t="n">
         <v>2.5</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>35</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1331,7 +1355,7 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1385,7 +1409,9 @@
       <c r="M14" t="n">
         <v>6.9</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1396,7 +1422,7 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1450,7 +1476,9 @@
       <c r="M15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1461,7 +1489,7 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1515,7 +1543,9 @@
       <c r="M16" t="n">
         <v>14.5</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>15.9</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1584,7 +1614,9 @@
       <c r="M17" t="n">
         <v>16.4</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -1595,7 +1627,7 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -1653,7 +1685,9 @@
       <c r="M18" t="n">
         <v>23.2</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>48.2</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1664,7 +1698,7 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1718,7 +1752,9 @@
       <c r="M19" t="n">
         <v>11.1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>28.2</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -1783,7 +1819,9 @@
       <c r="M20" t="n">
         <v>68.3</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>40.9</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1794,7 +1832,7 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -1852,7 +1890,9 @@
       <c r="M21" t="n">
         <v>9</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>18.7</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1863,7 +1903,7 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
@@ -1921,7 +1961,9 @@
       <c r="M22" t="n">
         <v>25.2</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>25.3</v>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1932,7 +1974,7 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -1990,7 +2032,9 @@
       <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>16.1</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -2001,7 +2045,7 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
@@ -2059,7 +2103,9 @@
       <c r="M24" t="n">
         <v>2.6</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>22.6</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2070,7 +2116,7 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2124,7 +2170,9 @@
       <c r="M25" t="n">
         <v>5</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -2135,7 +2183,7 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2189,7 +2237,9 @@
       <c r="M26" t="n">
         <v>1.9</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2200,7 +2250,7 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
@@ -2258,7 +2308,9 @@
       <c r="M27" t="n">
         <v>10.9</v>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>41</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2327,7 +2379,9 @@
       <c r="M28" t="n">
         <v>8.9</v>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>52.5</v>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -2338,7 +2392,7 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2392,7 +2446,9 @@
       <c r="M29" t="n">
         <v>5.6</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>43.6</v>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2403,7 +2459,7 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>96.5</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2457,7 +2513,9 @@
       <c r="M30" t="n">
         <v>21.8</v>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>16.6</v>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -2468,7 +2526,7 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
@@ -2530,7 +2588,9 @@
       <c r="M31" t="n">
         <v>14.4</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>29.8</v>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -2541,7 +2601,7 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2595,7 +2655,9 @@
       <c r="M32" t="n">
         <v>10</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>12.8</v>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -2606,7 +2668,7 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
@@ -2664,7 +2726,9 @@
       <c r="M33" t="n">
         <v>3.7</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>22.7</v>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -2675,7 +2739,7 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
@@ -2733,7 +2797,9 @@
       <c r="M34" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -2744,7 +2810,7 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
@@ -2798,7 +2864,9 @@
       <c r="M35" t="n">
         <v>5.5</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>26.3</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -2809,7 +2877,7 @@
         </is>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
@@ -2867,7 +2935,9 @@
       <c r="M36" t="n">
         <v>6.5</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>13.6</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -2878,7 +2948,7 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
@@ -2936,7 +3006,9 @@
       <c r="M37" t="n">
         <v>11.2</v>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>19.8</v>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -2947,7 +3019,7 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
@@ -3009,7 +3081,9 @@
       <c r="M38" t="n">
         <v>8.1</v>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>22.3</v>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -3020,7 +3094,7 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
@@ -3074,7 +3148,9 @@
       <c r="M39" t="n">
         <v>12.1</v>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -3085,7 +3161,7 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
@@ -3143,7 +3219,9 @@
       <c r="M40" t="n">
         <v>7.5</v>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>29.3</v>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -3212,7 +3290,9 @@
       <c r="M41" t="n">
         <v>6.7</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>24.6</v>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -3223,7 +3303,7 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
@@ -3279,7 +3359,9 @@
       <c r="M42" t="n">
         <v>7</v>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>11.5</v>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -3290,7 +3372,7 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
@@ -3352,7 +3434,9 @@
       <c r="M43" t="n">
         <v>15.9</v>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>13</v>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -3363,7 +3447,7 @@
         </is>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
@@ -3425,7 +3509,9 @@
       <c r="M44" t="n">
         <v>12.3</v>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>14.3</v>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -3436,7 +3522,7 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
@@ -3492,7 +3578,9 @@
       <c r="M45" t="n">
         <v>8.1</v>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>6</v>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -3503,7 +3591,7 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
@@ -3565,7 +3653,9 @@
       <c r="M46" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>34.9</v>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -3576,7 +3666,7 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
@@ -3638,7 +3728,9 @@
       <c r="M47" t="n">
         <v>10.4</v>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>13.2</v>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -3649,7 +3741,7 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -3711,7 +3803,9 @@
       <c r="M48" t="n">
         <v>-5.2</v>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>17.3</v>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -3722,7 +3816,7 @@
         </is>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -3784,7 +3878,9 @@
       <c r="M49" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>11.5</v>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -3795,7 +3891,7 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -3857,7 +3953,9 @@
       <c r="M50" t="n">
         <v>4.1</v>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -3868,7 +3966,7 @@
         </is>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -3928,7 +4026,9 @@
       <c r="M51" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>35.1</v>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
@@ -3939,7 +4039,7 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -3999,7 +4099,9 @@
       <c r="M52" t="n">
         <v>-3.9</v>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -4010,7 +4112,7 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
@@ -4203,7 +4305,9 @@
       <c r="M2" t="n">
         <v>11.8</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>31.8</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -4214,7 +4318,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -4268,7 +4372,9 @@
       <c r="M3" t="n">
         <v>11.8</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -4279,7 +4385,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -4333,7 +4439,9 @@
       <c r="M4" t="n">
         <v>13.8</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>27.3</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -4344,7 +4452,7 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -4398,7 +4506,9 @@
       <c r="M5" t="n">
         <v>14.3</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>23.5</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -4409,7 +4519,7 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -4467,7 +4577,9 @@
       <c r="M6" t="n">
         <v>24.8</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -4478,7 +4590,7 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -4532,7 +4644,9 @@
       <c r="M7" t="n">
         <v>13.2</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>35.7</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -4601,7 +4715,9 @@
       <c r="M8" t="n">
         <v>10.8</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -4666,7 +4782,9 @@
       <c r="M9" t="n">
         <v>17.5</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>32.2</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -4735,7 +4853,9 @@
       <c r="M10" t="n">
         <v>12.6</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -4746,7 +4866,7 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
@@ -4804,7 +4924,9 @@
       <c r="M11" t="n">
         <v>6.9</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>7.7</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -4815,7 +4937,7 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -4873,7 +4995,9 @@
       <c r="M12" t="n">
         <v>18.2</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>18.7</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -4884,7 +5008,7 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -4938,7 +5062,9 @@
       <c r="M13" t="n">
         <v>2.5</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>35</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -4949,7 +5075,7 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -5003,7 +5129,9 @@
       <c r="M14" t="n">
         <v>6.9</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -5014,7 +5142,7 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -5068,7 +5196,9 @@
       <c r="M15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -5079,7 +5209,7 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -5133,7 +5263,9 @@
       <c r="M16" t="n">
         <v>14.5</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>15.9</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -5202,7 +5334,9 @@
       <c r="M17" t="n">
         <v>16.4</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -5213,7 +5347,7 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -5271,7 +5405,9 @@
       <c r="M18" t="n">
         <v>23.2</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>48.2</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -5282,7 +5418,7 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -5336,7 +5472,9 @@
       <c r="M19" t="n">
         <v>11.1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>28.2</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -5401,7 +5539,9 @@
       <c r="M20" t="n">
         <v>68.3</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>40.9</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -5412,7 +5552,7 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -5732,7 +5872,9 @@
       <c r="M2" t="n">
         <v>14.3</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>23.5</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -5743,7 +5885,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
@@ -5801,7 +5943,9 @@
       <c r="M3" t="n">
         <v>13.2</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>35.7</v>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -5870,7 +6014,9 @@
       <c r="M4" t="n">
         <v>17.5</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>32.2</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -5939,7 +6085,9 @@
       <c r="M5" t="n">
         <v>12.6</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>19.9</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -5950,7 +6098,7 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -6008,7 +6156,9 @@
       <c r="M6" t="n">
         <v>6.9</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>7.7</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -6019,7 +6169,7 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
@@ -6077,7 +6227,9 @@
       <c r="M7" t="n">
         <v>14.5</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>15.9</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -6146,7 +6298,9 @@
       <c r="M8" t="n">
         <v>16.4</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -6157,7 +6311,7 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -6215,7 +6369,9 @@
       <c r="M9" t="n">
         <v>68.3</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>40.9</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -6226,7 +6382,7 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
@@ -6284,7 +6440,9 @@
       <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>18.7</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -6295,7 +6453,7 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
@@ -6353,7 +6511,9 @@
       <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>16.1</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -6364,7 +6524,7 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
@@ -6422,7 +6582,9 @@
       <c r="M12" t="n">
         <v>1.9</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -6433,7 +6595,7 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
@@ -6491,7 +6653,9 @@
       <c r="M13" t="n">
         <v>21.8</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>16.6</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -6502,7 +6666,7 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
@@ -6564,7 +6728,9 @@
       <c r="M14" t="n">
         <v>10</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>12.8</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -6575,7 +6741,7 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
@@ -6633,7 +6799,9 @@
       <c r="M15" t="n">
         <v>11.2</v>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>19.8</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -6644,7 +6812,7 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
@@ -6706,7 +6874,9 @@
       <c r="M16" t="n">
         <v>12.1</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -6717,7 +6887,7 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
@@ -6773,7 +6943,9 @@
       <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>11.5</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -6784,7 +6956,7 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
@@ -6846,7 +7018,9 @@
       <c r="M18" t="n">
         <v>15.9</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>13</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -6857,7 +7031,7 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
@@ -6917,7 +7091,9 @@
       <c r="M19" t="n">
         <v>8.1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -6928,7 +7104,7 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
@@ -6990,7 +7166,9 @@
       <c r="M20" t="n">
         <v>10.7</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>34.9</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -7001,7 +7179,7 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
@@ -7063,7 +7241,9 @@
       <c r="M21" t="n">
         <v>10.4</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>13.2</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -7074,7 +7254,7 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
@@ -7136,7 +7316,9 @@
       <c r="M22" t="n">
         <v>-5.2</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>17.3</v>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -7147,7 +7329,7 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
@@ -7209,7 +7391,9 @@
       <c r="M23" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>11.5</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -7220,7 +7404,7 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
@@ -7282,7 +7466,9 @@
       <c r="M24" t="n">
         <v>4.1</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -7293,7 +7479,7 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
@@ -7353,7 +7539,9 @@
       <c r="M25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>35.1</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -7364,7 +7552,7 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
@@ -7424,7 +7612,9 @@
       <c r="M26" t="n">
         <v>-3.9</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>10.7</v>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -7435,7 +7625,7 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
